--- a/quests/GuildWars_PostSearing_Ascalon.xlsx
+++ b/quests/GuildWars_PostSearing_Ascalon.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Post-Searing Ascalon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Post-Searing Ascalon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3033,6 +3033,166 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Surviving After the Searing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Warmaster Tydus</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ascalon City</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Reforged Mode</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1000 XP, 500g, 4 Skill Points, Sup. Kits</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Elegy for Those Left Behind</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ghost of Althea</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>The Breach</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Reforged Mode, Althea's Ashes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>500 XP, 100g</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>The Cost of Survival</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Kopp the Quick</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Piken Square</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Elegy for Those Left Behind</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>500 XP, 100g</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>The Dreamer and the Zealot</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ghost of Althea</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tunnels of the Forsaken</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>The Cost of Survival</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1000 XP, 100g, Ghost of Althea (Hero)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
